--- a/public/plantilla-viajes.xlsx
+++ b/public/plantilla-viajes.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Viajes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="LOV" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Instrucciones" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,11 +32,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="006B7280"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -97,28 +93,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -205,20 +196,25 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Agrupa filas del mismo viaje (V1, V2...). La primera fila de cada Viaje completa Fecha/Hora/Categoria/Pasajeros. Las siguientes filas con el mismo Viaje se interpretan como tramos adicionales.</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>Multiples pasajeros separados por  |  (ej: R. Mendez | M. Rios). Maximo 4.</t>
+        <t>Dia / Mes / Año: completar solo con numeros (ej: 19 / 6 / 2026).</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>in = llegada (con vuelo)
-out = salida (con vuelo)
-otro = traslado
-disposicion = horas a disposicion</t>
+        <t>Varios pasajeros separados por  |  (ej: M. Rojo | N. Fabbri). Maximo 4.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Llegada (in) = arribo con vuelo
+Salida (out) = salida con vuelo
+Hs Disposición = horas a disposicion
+Otro = traslado</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Destino 2 / Destino 3: tramos adicionales del mismo viaje. Dejar vacio si el viaje tiene un solo tramo.</t>
       </text>
     </comment>
   </commentList>
@@ -514,398 +510,380 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Viaje</t>
+          <t>Dia</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Fecha</t>
+          <t>Mes</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Pasajeros</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Telefono</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Origen</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Destino</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Vuelo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Destino 2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Destino 3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>V1</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Ejecutivo</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>R. Mendez</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Recoleta</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>JUAN PABLO VOJVODA</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>+54 9 11 5555-1234</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Llegada (in)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Aeropuerto Ezeiza (EZE)</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>AA995</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>725 Continental</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>AR1234</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>V2</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="A3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Auto Std</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>M. ROJO | N. FABBRI</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>+54 9 11 5555-2256</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Salida (out)</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Santos Dumont 3429</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Aeropuerto Ezeiza (EZE)</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>AR1256</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>CHAQUEÑO PALAVECINO</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>+54 9 387 555-1456</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Salida (out)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Balcarce 230, Salta</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Aeropuerto de Salta</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>AR1456</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Vito</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>MARTÍN ROMAGNOLI</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>+54 9 11 5555-4302</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Hotel Faena</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Hotel Alvear</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Pasa a buscar valijas</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>San Isidro</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Ejecutivo</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>K. Nunez | M. Rios</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>Aeroparque Jorge Newbery (AEP)</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>V3</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>MiniVan</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>S. Vega | A. Soto | J. Pereyra</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>otro</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Tigre</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Microcentro</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Reservar 3 valijas</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>V3</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>otro</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Microcentro</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Puerto Madero</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>V4</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Auto STD</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>L. Bravo</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Aeroparque Jorge Newbery (AEP)</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>Hotel Faena</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>LA4302</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>V4</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>otro</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Hotel Faena</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>San Isidro</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>V4</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>San Isidro</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>Aeropuerto Ezeiza (EZE)</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>AA996</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>V5</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Ejecutivo</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>F. Acosta</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>disposicion</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>F. ACOSTA</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>+54 9 11 5555-7788</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Hs Disposición</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Hotel Alvear</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Hotel Alvear</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>4 hs disposicion</t>
-        </is>
-      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>4 hs a disposicion</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="H2:H200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elegi un Tipo de la lista." prompt="Elegi: Llegada (in) / Salida (out) / Hs Disposición / Otro" type="list">
+      <formula1>=LOV!$A$2:$A$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elegi una Categoria de la lista." prompt="Elegi: Auto Std / Ejecutivo / MB / Vito" type="list">
+      <formula1>=LOV!$B$2:$B$5</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -917,123 +895,225 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Llegada (in)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Auto Std</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Salida (out)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ejecutivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Hs Disposición</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Vito</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="92" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Plantilla de carga de viajes</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Hoja Viajes</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Una fila por TRAMO. Para varios tramos del mismo viaje, repeti el ID de Viaje.</t>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Una fila por VIAJE. Para tramos adicionales usa las columnas Destino 2 y Destino 3.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Viaje</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Identificador interno del viaje (V1, V2, ...). Agrupa tramos.</t>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Dia / Mes / Año</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Completar los tres campos solo con numeros (ej: 19 / 6 / 2026).</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Fecha / Hora</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Solo en la PRIMERA fila de cada Viaje. Formato Fecha YYYY-MM-DD, Hora HH:MM (24h).</t>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Hora</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Formato HH:MM en 24 horas (ej: 07:30).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Auto STD / Ejecutivo / MiniVan. Solo en la primera fila del Viaje.</t>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Elegir del desplegable: Auto Std / Ejecutivo / MB / Vito.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Pasajeros</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Solo en la primera fila. Separa varios pasajeros con  |  (pipe). Maximo 4.</t>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Nombre del pasajero. Varios separados con  |  (pipe). Maximo 4.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Telefono</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Telefono valido del pasajero principal (ej: +54 9 11 5555-1234).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>in = llegada con vuelo · out = salida con vuelo · otro = traslado · disposicion = horas a disposicion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Llegada (in) = arribo con vuelo · Salida (out) = salida con vuelo · Hs Disposición = horas a disposicion · Otro = traslado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Origen / Destino</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Direccion o lugar. En tramos siguientes, Origen suele coincidir con el Destino anterior.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Direccion o lugar (el sistema usa Google Maps para geolocalizar la direccion).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Destino 2 / Destino 3</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Tramos adicionales del mismo viaje. Dejar vacio si hay un solo tramo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Vuelo</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Solo para tipo in / out (ej: AA995). Dejar vacio en otros casos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Solo para tipo Llegada (in) / Salida (out), ej: AR1234. Dejar vacio en otros casos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Texto libre opcional.</t>
         </is>

--- a/public/plantilla-viajes.xlsx
+++ b/public/plantilla-viajes.xlsx
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Un telefono por pasajero, en el mismo orden que Pasajeros, separados con  |  (ej: +54 9 11 4490-7781 | +54 9 11 6033-2210).</t>
+          <t>OBLIGATORIO. Un telefono por pasajero, en el mismo orden que Pasajeros, separados con  |  (ej: +54 9 11 4490-7781 | +54 9 11 6033-2210).</t>
         </is>
       </c>
     </row>

--- a/public/plantilla-viajes.xlsx
+++ b/public/plantilla-viajes.xlsx
@@ -18,7 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -93,12 +96,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -196,20 +205,20 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Dia / Mes / Año: completar solo con numeros (ej: 19 / 6 / 2026).</t>
+        <t>Fecha del viaje en formato DD/MM/AAAA (ej: 19/06/2026).</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <t>Varios pasajeros separados por  |  (ej: M. Rojo | N. Fabbri). Maximo 4.</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <t>Un telefono por pasajero, en el MISMO orden y separados por  |  (ej: +54 9 11 4490-7781 | +54 9 11 6033-2210).</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t>Llegada (in) = arribo con vuelo
 Salida (out) = salida con vuelo
@@ -217,7 +226,7 @@
 Otro = traslado</t>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <t>Destino 2 / Destino 3: tramos adicionales del mismo viaje. Dejar vacio si el viaje tiene un solo tramo.</t>
       </text>
@@ -515,92 +524,80 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dia</t>
+          <t>Fecha</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Mes</t>
+          <t>Hora</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Año</t>
+          <t>Categoria</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>Pasajeros</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Categoria</t>
+          <t>Telefono</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Pasajeros</t>
+          <t>Tipo</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Telefono</t>
+          <t>Origen</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Tipo</t>
+          <t>Destino</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Origen</t>
+          <t>Vuelo</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Destino</t>
+          <t>Observaciones</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Vuelo</t>
+          <t>Destino 2</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Observaciones</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Destino 2</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Destino 3</t>
         </is>
@@ -608,284 +605,254 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+        <v>46255</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Ejecutivo</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>JUAN PABLO VOJVODA</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>+54 9 11 5555-1234</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Llegada (in)</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Aeropuerto Ezeiza (EZE)</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>725 Continental</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>AR1234</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Auto Std</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>M. ROJO | N. FABBRI</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>+54 9 11 4490-7781 | +54 9 11 6033-2210</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Salida (out)</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Santos Dumont 3429</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Aeropuerto Ezeiza (EZE)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>AR1256</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+        <v>46255</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>MB</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>CHAQUEÑO PALAVECINO</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>+54 9 387 555-1456</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Salida (out)</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Balcarce 230, Salta</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Aeropuerto de Salta</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>AR1456</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Vito</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>MARTÍN ROMAGNOLI</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>+54 9 11 5555-4302</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Otro</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Hotel Faena</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Hotel Alvear</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Pasa a buscar valijas</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>San Isidro</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr"/>
+      <c r="L5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+        <v>46255</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Ejecutivo</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>F. ACOSTA</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>+54 9 11 5555-7788</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Hs Disposición</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Hotel Alvear</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Hotel Alvear</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>4 hs a disposicion</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elegi un Tipo de la lista." prompt="Elegi: Llegada (in) / Salida (out) / Hs Disposición / Otro" type="list">
+    <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elegi un Tipo de la lista." prompt="Elegi: Llegada (in) / Salida (out) / Hs Disposición / Otro" type="list">
       <formula1>=LOV!$A$2:$A$5</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elegi una Categoria de la lista." prompt="Elegi: Auto Std / Ejecutivo / MB / Vito" type="list">
+    <dataValidation sqref="C2:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elegi una Categoria de la lista." prompt="Elegi: Auto Std / Ejecutivo / MB / Vito" type="list">
       <formula1>=LOV!$B$2:$B$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -908,12 +875,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
@@ -986,139 +953,139 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Plantilla de carga de viajes</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Hoja Viajes</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Una fila por VIAJE. Para tramos adicionales usa las columnas Destino 2 y Destino 3.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Dia / Mes / Año</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Completar los tres campos solo con numeros (ej: 19 / 6 / 2026).</t>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Fecha del viaje en formato DD/MM/AAAA (ej: 19/06/2026).</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Formato HH:MM en 24 horas (ej: 07:30).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Elegir del desplegable: Auto Std / Ejecutivo / MB / Vito.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Pasajeros</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Nombre del pasajero. Varios separados con  |  (pipe). Maximo 4.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Telefono</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>OBLIGATORIO. Un telefono por pasajero, en el mismo orden que Pasajeros, separados con  |  (ej: +54 9 11 4490-7781 | +54 9 11 6033-2210).</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Llegada (in) = arribo con vuelo · Salida (out) = salida con vuelo · Hs Disposición = horas a disposicion · Otro = traslado.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Origen / Destino</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Direccion o lugar (el sistema usa Google Maps para geolocalizar la direccion).</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Destino 2 / Destino 3</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Tramos adicionales del mismo viaje. Dejar vacio si hay un solo tramo.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Vuelo</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Solo para tipo Llegada (in) / Salida (out), ej: AR1234. Dejar vacio en otros casos.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Texto libre opcional.</t>
         </is>

--- a/public/plantilla-viajes.xlsx
+++ b/public/plantilla-viajes.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Viajes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="LOV" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="LOV" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet name="Instrucciones" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -18,9 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="166" formatCode="HH:MM"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -29,6 +30,12 @@
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -43,16 +50,10 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001F2937"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -62,11 +63,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F3F4F6"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,29 +92,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -195,44 +192,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Plantilla</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>Fecha del viaje en formato DD/MM/AAAA (ej: 19/06/2026).</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>Varios pasajeros separados por  |  (ej: M. Rojo | N. Fabbri). Maximo 4.</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>Un telefono por pasajero, en el MISMO orden y separados por  |  (ej: +54 9 11 4490-7781 | +54 9 11 6033-2210).</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>Llegada (in) = arribo con vuelo
-Salida (out) = salida con vuelo
-Hs Disposición = horas a disposicion
-Otro = traslado</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>Destino 2 / Destino 3: tramos adicionales del mismo viaje. Dejar vacio si el viaje tiene un solo tramo.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -524,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A2:L64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -541,323 +500,1100 @@
     <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Hora</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Categoria</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Pasajeros</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Telefono</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Origen</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Destino</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Vuelo</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Observaciones</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Destino 2</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Destino 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>46255</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>INCOMING HUB | PLANTILLA SERVICIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>HORA</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>CATEGORÍA</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>TELÉFONO</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>ORIGEN</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>DESTINO</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>VUELO</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>OBSERVACIONES</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>DESTINO 2</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>DESTINO 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="27" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Ejecutivo</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>JUAN PABLO VOJVODA</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>JUAN LÓPEZ</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>+54 9 11 5555-1234</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Llegada (in)</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Aeropuerto Ezeiza (EZE)</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>725 Continental</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>AR1234</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr"/>
-      <c r="K2" s="3" t="inlineStr"/>
-      <c r="L2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="n">
-        <v>46255</v>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>AEROPUERTO EZEIZA (EZE)</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>725 CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>AA 909</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Auto Std</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>M. ROJO | N. FABBRI</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>+54 9 11 4490-7781 | +54 9 11 6033-2210</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>MARÍA CÁCERES | N. FABBRI</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>+54 9 11 5555-1234 | +54 9 11 6033-2210</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Salida (out)</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Santos Dumont 3429</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>Aeropuerto Ezeiza (EZE)</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>SANTOS DUMONT 3429, CABA</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>AEROPARQUE (AEP)</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>AR1256</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr"/>
-      <c r="L3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>46255</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>OFICINA</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Vito</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>LUCAS GARIBALDI</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>+54 9 387 555-1456</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Salida (out)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>MARRIOT PLAZA</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>AEROPUERTO EZEIZA (EZE)</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>AR1456</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Ejecutivo</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>ELISA BARÓ</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>+54 9 11 5555-4302</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>HOTEL FAENA</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>HOTEL FAENA</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>CITY TOUR</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>PUERTO MADERO</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>HOTEL FAENA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="3" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>MB</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>CHAQUEÑO PALAVECINO</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>+54 9 387 555-1456</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Salida (out)</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Balcarce 230, Salta</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Aeropuerto de Salta</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>AR1456</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>46255</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Vito</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>MARTÍN ROMAGNOLI</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>+54 9 11 5555-4302</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Otro</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Hotel Faena</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Hotel Alvear</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>Pasa a buscar valijas</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>San Isidro</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>46255</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Ejecutivo</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>F. ACOSTA</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>+54 9 11 5555-7788</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Hs Disposición</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Hotel Alvear</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Hotel Alvear</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>4 hs a disposicion</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>HOTEL ALVEAR</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>HOTEL ALVEAR</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>4 HS A DISPOSICIÓN</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="3" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="27" customHeight="1">
+      <c r="A12" s="3" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="27" customHeight="1">
+      <c r="A14" s="3" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="27" customHeight="1">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="27" customHeight="1">
+      <c r="A16" s="3" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="27" customHeight="1">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="27" customHeight="1">
+      <c r="A18" s="3" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="27" customHeight="1">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="3" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="27" customHeight="1">
+      <c r="A21" s="3" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="27" customHeight="1">
+      <c r="A22" s="3" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="27" customHeight="1">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="27" customHeight="1">
+      <c r="A24" s="3" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="27" customHeight="1">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="27" customHeight="1">
+      <c r="A26" s="3" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="27" customHeight="1">
+      <c r="A27" s="3" t="n"/>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="27" customHeight="1">
+      <c r="A28" s="3" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="27" customHeight="1">
+      <c r="A29" s="3" t="n"/>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="27" customHeight="1">
+      <c r="A30" s="3" t="n"/>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="27" customHeight="1">
+      <c r="A31" s="3" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="27" customHeight="1">
+      <c r="A32" s="3" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="27" customHeight="1">
+      <c r="A33" s="3" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="27" customHeight="1">
+      <c r="A34" s="3" t="n"/>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="27" customHeight="1">
+      <c r="A35" s="3" t="n"/>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="5" t="n"/>
+    </row>
+    <row r="36" ht="27" customHeight="1">
+      <c r="A36" s="3" t="n"/>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="27" customHeight="1">
+      <c r="A37" s="3" t="n"/>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="27" customHeight="1">
+      <c r="A38" s="3" t="n"/>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="27" customHeight="1">
+      <c r="A39" s="3" t="n"/>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="n"/>
+      <c r="L39" s="5" t="n"/>
+    </row>
+    <row r="40" ht="27" customHeight="1">
+      <c r="A40" s="3" t="n"/>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="5" t="n"/>
+    </row>
+    <row r="41" ht="27" customHeight="1">
+      <c r="A41" s="3" t="n"/>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="5" t="n"/>
+    </row>
+    <row r="42" ht="27" customHeight="1">
+      <c r="A42" s="3" t="n"/>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+    </row>
+    <row r="43" ht="27" customHeight="1">
+      <c r="A43" s="3" t="n"/>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="n"/>
+      <c r="L43" s="5" t="n"/>
+    </row>
+    <row r="44" ht="27" customHeight="1">
+      <c r="A44" s="3" t="n"/>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+    </row>
+    <row r="45" ht="27" customHeight="1">
+      <c r="A45" s="3" t="n"/>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+    </row>
+    <row r="46" ht="27" customHeight="1">
+      <c r="A46" s="3" t="n"/>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+    </row>
+    <row r="47" ht="27" customHeight="1">
+      <c r="A47" s="3" t="n"/>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="n"/>
+    </row>
+    <row r="48" ht="27" customHeight="1">
+      <c r="A48" s="3" t="n"/>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n"/>
+    </row>
+    <row r="49" ht="27" customHeight="1">
+      <c r="A49" s="3" t="n"/>
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="n"/>
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="5" t="n"/>
+    </row>
+    <row r="50" ht="27" customHeight="1">
+      <c r="A50" s="3" t="n"/>
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="5" t="n"/>
+    </row>
+    <row r="51" ht="27" customHeight="1">
+      <c r="A51" s="3" t="n"/>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+    </row>
+    <row r="52" ht="27" customHeight="1">
+      <c r="A52" s="3" t="n"/>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n"/>
+    </row>
+    <row r="53" ht="27" customHeight="1">
+      <c r="A53" s="3" t="n"/>
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="n"/>
+      <c r="L53" s="5" t="n"/>
+    </row>
+    <row r="54" ht="27" customHeight="1">
+      <c r="A54" s="3" t="n"/>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="5" t="n"/>
+    </row>
+    <row r="55" ht="27" customHeight="1">
+      <c r="A55" s="3" t="n"/>
+      <c r="B55" s="4" t="n"/>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="n"/>
+      <c r="L55" s="5" t="n"/>
+    </row>
+    <row r="56" ht="27" customHeight="1">
+      <c r="A56" s="3" t="n"/>
+      <c r="B56" s="4" t="n"/>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
+      <c r="K56" s="5" t="n"/>
+      <c r="L56" s="5" t="n"/>
+    </row>
+    <row r="57" ht="27" customHeight="1">
+      <c r="A57" s="3" t="n"/>
+      <c r="B57" s="4" t="n"/>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="n"/>
+    </row>
+    <row r="58" ht="27" customHeight="1">
+      <c r="A58" s="3" t="n"/>
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="5" t="n"/>
+    </row>
+    <row r="59" ht="27" customHeight="1">
+      <c r="A59" s="3" t="n"/>
+      <c r="B59" s="4" t="n"/>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="5" t="n"/>
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
+      <c r="K59" s="5" t="n"/>
+      <c r="L59" s="5" t="n"/>
+    </row>
+    <row r="60" ht="27" customHeight="1">
+      <c r="A60" s="3" t="n"/>
+      <c r="B60" s="4" t="n"/>
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n"/>
+    </row>
+    <row r="61" ht="27" customHeight="1">
+      <c r="A61" s="3" t="n"/>
+      <c r="B61" s="4" t="n"/>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+    </row>
+    <row r="62" ht="27" customHeight="1">
+      <c r="A62" s="3" t="n"/>
+      <c r="B62" s="4" t="n"/>
+      <c r="C62" s="5" t="n"/>
+      <c r="D62" s="5" t="n"/>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="n"/>
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="5" t="n"/>
+      <c r="I62" s="5" t="n"/>
+      <c r="J62" s="5" t="n"/>
+      <c r="K62" s="5" t="n"/>
+      <c r="L62" s="5" t="n"/>
+    </row>
+    <row r="63" ht="27" customHeight="1">
+      <c r="A63" s="3" t="n"/>
+      <c r="B63" s="4" t="n"/>
+      <c r="C63" s="5" t="n"/>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="n"/>
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="5" t="n"/>
+      <c r="I63" s="5" t="n"/>
+      <c r="J63" s="5" t="n"/>
+      <c r="K63" s="5" t="n"/>
+      <c r="L63" s="5" t="n"/>
+    </row>
+    <row r="64" ht="27" customHeight="1">
+      <c r="A64" s="3" t="n"/>
+      <c r="B64" s="4" t="n"/>
+      <c r="C64" s="5" t="n"/>
+      <c r="D64" s="5" t="n"/>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="n"/>
+      <c r="G64" s="5" t="n"/>
+      <c r="H64" s="5" t="n"/>
+      <c r="I64" s="5" t="n"/>
+      <c r="J64" s="5" t="n"/>
+      <c r="K64" s="5" t="n"/>
+      <c r="L64" s="5" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:L2"/>
+  </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elegi un Tipo de la lista." prompt="Elegi: Llegada (in) / Salida (out) / Hs Disposición / Otro" type="list">
+    <dataValidation sqref="F5:F203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elegí un Tipo de la lista." prompt="Elegí: Llegada (in) / Salida (out) / Hs Disposición / Otro" type="list">
       <formula1>=LOV!$A$2:$A$5</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elegi una Categoria de la lista." prompt="Elegi: Auto Std / Ejecutivo / MB / Vito" type="list">
+    <dataValidation sqref="C5:C203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elegí una Categoría de la lista." prompt="Elegí: Auto Std / Ejecutivo / MB / Vito" type="list">
       <formula1>=LOV!$B$2:$B$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -887,48 +1623,48 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Llegada (in)</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Auto Std</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Salida (out)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Ejecutivo</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Hs Disposición</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>MB</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Otro</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Vito</t>
         </is>
@@ -948,144 +1684,144 @@
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="92" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>Plantilla de carga de viajes</t>
+    <row r="1" ht="31" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>INCOMING HUB | PLANTILLA SERVICIOS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>Hoja Viajes</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Una fila por VIAJE. Para tramos adicionales usa las columnas Destino 2 y Destino 3.</t>
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>HOJA VIAJES</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Una fila por VIAJE. Para tramos adicionales usá las columnas DESTINO 2 y DESTINO 3. Las filas de ejemplo se pueden borrar o pisar.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>Fecha del viaje en formato DD/MM/AAAA (ej: 19/06/2026).</t>
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Formato día/mes/año (ej: 10/09/2026).</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Hora</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>HORA</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Formato HH:MM en 24 horas (ej: 07:30).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Categoria</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>CATEGORÍA</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Elegir del desplegable: Auto Std / Ejecutivo / MB / Vito.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Pasajeros</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Nombre del pasajero. Varios separados con  |  (pipe). Maximo 4.</t>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Nombre del pasajero. Varios separados con  |  (pipe). Máximo 4.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Telefono</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>OBLIGATORIO. Un telefono por pasajero, en el mismo orden que Pasajeros, separados con  |  (ej: +54 9 11 4490-7781 | +54 9 11 6033-2210).</t>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>TELÉFONO</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>OBLIGATORIO. Un teléfono por pasajero, en el mismo orden que PAX, separados con  |  (ej: +54 9 11 4490-7781 | +54 9 11 6033-2210).</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Llegada (in) = arribo con vuelo · Salida (out) = salida con vuelo · Hs Disposición = horas a disposicion · Otro = traslado.</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Llegada (in) = arribo con vuelo · Salida (out) = salida con vuelo · Hs Disposición = horas a disposición · Otro = traslado.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Origen / Destino</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Direccion o lugar (el sistema usa Google Maps para geolocalizar la direccion).</t>
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>ORIGEN / DESTINO</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Dirección o lugar (el sistema usa Google Maps para geolocalizar la dirección).</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Destino 2 / Destino 3</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Tramos adicionales del mismo viaje. Dejar vacio si hay un solo tramo.</t>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>DESTINO 2 / DESTINO 3</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Tramos adicionales del mismo viaje. Dejar vacío si hay un solo tramo.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Vuelo</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Solo para tipo Llegada (in) / Salida (out), ej: AR1234. Dejar vacio en otros casos.</t>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>VUELO</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Solo para tipo Llegada (in) / Salida (out), ej: AR1234. Dejar vacío en otros casos.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Observaciones</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>OBSERVACIONES</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Texto libre opcional.</t>
         </is>
